--- a/R_Codes/DataSummary/Bacteria/Sample_name/Bacteria_Summary_Phylum_by_Sample_name.xlsx
+++ b/R_Codes/DataSummary/Bacteria/Sample_name/Bacteria_Summary_Phylum_by_Sample_name.xlsx
@@ -577,10 +577,10 @@
         <v>5</v>
       </c>
       <c r="C2" t="n">
-        <v>27.1997099190021</v>
+        <v>27.1987993565221</v>
       </c>
       <c r="D2" t="n">
-        <v>0.506917775226986</v>
+        <v>0.508382267579577</v>
       </c>
     </row>
     <row r="3">
@@ -591,10 +591,10 @@
         <v>6</v>
       </c>
       <c r="C3" t="n">
-        <v>15.4888037517245</v>
+        <v>15.4954749533721</v>
       </c>
       <c r="D3" t="n">
-        <v>0.179534688608049</v>
+        <v>0.179619814516198</v>
       </c>
     </row>
     <row r="4">
@@ -605,10 +605,10 @@
         <v>7</v>
       </c>
       <c r="C4" t="n">
-        <v>13.229222995601</v>
+        <v>13.2259113259634</v>
       </c>
       <c r="D4" t="n">
-        <v>0.332041037402572</v>
+        <v>0.331855277381578</v>
       </c>
     </row>
     <row r="5">
@@ -619,10 +619,10 @@
         <v>8</v>
       </c>
       <c r="C5" t="n">
-        <v>8.028736127089</v>
+        <v>8.02835388683251</v>
       </c>
       <c r="D5" t="n">
-        <v>0.22815794261945</v>
+        <v>0.228047101254038</v>
       </c>
     </row>
     <row r="6">
@@ -633,10 +633,10 @@
         <v>9</v>
       </c>
       <c r="C6" t="n">
-        <v>5.08320583243194</v>
+        <v>5.08912035619873</v>
       </c>
       <c r="D6" t="n">
-        <v>0.583759201446353</v>
+        <v>0.584684683049469</v>
       </c>
     </row>
     <row r="7">
@@ -647,10 +647,10 @@
         <v>10</v>
       </c>
       <c r="C7" t="n">
-        <v>5.04944993052281</v>
+        <v>5.05007687408811</v>
       </c>
       <c r="D7" t="n">
-        <v>0.116212896021414</v>
+        <v>0.116185975312037</v>
       </c>
     </row>
     <row r="8">
@@ -661,10 +661,10 @@
         <v>11</v>
       </c>
       <c r="C8" t="n">
-        <v>3.77156599539515</v>
+        <v>3.75919096964261</v>
       </c>
       <c r="D8" t="n">
-        <v>0.772222734856447</v>
+        <v>0.820425756252473</v>
       </c>
     </row>
     <row r="9">
@@ -675,10 +675,10 @@
         <v>12</v>
       </c>
       <c r="C9" t="n">
-        <v>2.71536092622998</v>
+        <v>2.7168261433294</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0406410369178549</v>
+        <v>0.040682636861371</v>
       </c>
     </row>
     <row r="10">
@@ -689,10 +689,10 @@
         <v>13</v>
       </c>
       <c r="C10" t="n">
-        <v>2.15894967249864</v>
+        <v>2.15910343882614</v>
       </c>
       <c r="D10" t="n">
-        <v>0.0891871554359283</v>
+        <v>0.0891807023663215</v>
       </c>
     </row>
     <row r="11">
@@ -703,10 +703,10 @@
         <v>14</v>
       </c>
       <c r="C11" t="n">
-        <v>1.89041475746432</v>
+        <v>1.89088521201451</v>
       </c>
       <c r="D11" t="n">
-        <v>0.285295396610977</v>
+        <v>0.285391683730003</v>
       </c>
     </row>
     <row r="12">
@@ -717,10 +717,10 @@
         <v>15</v>
       </c>
       <c r="C12" t="n">
-        <v>1.88627177439202</v>
+        <v>1.88678565480708</v>
       </c>
       <c r="D12" t="n">
-        <v>0.098136639330658</v>
+        <v>0.0981585578519287</v>
       </c>
     </row>
     <row r="13">
@@ -731,10 +731,10 @@
         <v>16</v>
       </c>
       <c r="C13" t="n">
-        <v>1.75718275103475</v>
+        <v>1.75654445620912</v>
       </c>
       <c r="D13" t="n">
-        <v>0.130896501178287</v>
+        <v>0.130814247780952</v>
       </c>
     </row>
     <row r="14">
@@ -745,10 +745,10 @@
         <v>17</v>
       </c>
       <c r="C14" t="n">
-        <v>1.60111755367277</v>
+        <v>1.60118333763949</v>
       </c>
       <c r="D14" t="n">
-        <v>0.105181588341937</v>
+        <v>0.105196200186319</v>
       </c>
     </row>
     <row r="15">
@@ -759,10 +759,10 @@
         <v>18</v>
       </c>
       <c r="C15" t="n">
-        <v>1.50564927210976</v>
+        <v>1.5054470119865</v>
       </c>
       <c r="D15" t="n">
-        <v>0.256379238498371</v>
+        <v>0.25636445455321</v>
       </c>
     </row>
     <row r="16">
@@ -773,10 +773,10 @@
         <v>19</v>
       </c>
       <c r="C16" t="n">
-        <v>1.07809169025661</v>
+        <v>1.07756858112191</v>
       </c>
       <c r="D16" t="n">
-        <v>0.42393483508724</v>
+        <v>0.423728975821153</v>
       </c>
     </row>
     <row r="17">
@@ -787,10 +787,10 @@
         <v>20</v>
       </c>
       <c r="C17" t="n">
-        <v>0.835334189022212</v>
+        <v>0.836043950484312</v>
       </c>
       <c r="D17" t="n">
-        <v>0.131596510084183</v>
+        <v>0.131785520769416</v>
       </c>
     </row>
     <row r="18">
@@ -801,10 +801,10 @@
         <v>21</v>
       </c>
       <c r="C18" t="n">
-        <v>0.827129723079771</v>
+        <v>0.827446789219372</v>
       </c>
       <c r="D18" t="n">
-        <v>0.065711915353586</v>
+        <v>0.0656968424689267</v>
       </c>
     </row>
     <row r="19">
@@ -815,10 +815,10 @@
         <v>22</v>
       </c>
       <c r="C19" t="n">
-        <v>0.783297488670672</v>
+        <v>0.783369214878462</v>
       </c>
       <c r="D19" t="n">
-        <v>0.0762966507847234</v>
+        <v>0.076304611860434</v>
       </c>
     </row>
     <row r="20">
@@ -829,10 +829,10 @@
         <v>23</v>
       </c>
       <c r="C20" t="n">
-        <v>0.749659009917814</v>
+        <v>0.749516216573399</v>
       </c>
       <c r="D20" t="n">
-        <v>0.0571783094222008</v>
+        <v>0.0571555031807758</v>
       </c>
     </row>
     <row r="21">
@@ -843,10 +843,10 @@
         <v>24</v>
       </c>
       <c r="C21" t="n">
-        <v>0.496390789086711</v>
+        <v>0.496316629494725</v>
       </c>
       <c r="D21" t="n">
-        <v>0.0160652487514577</v>
+        <v>0.0160595372499291</v>
       </c>
     </row>
     <row r="22">
@@ -857,10 +857,10 @@
         <v>25</v>
       </c>
       <c r="C22" t="n">
-        <v>0.466972583887116</v>
+        <v>0.466936665839005</v>
       </c>
       <c r="D22" t="n">
-        <v>0.0355597834704603</v>
+        <v>0.0355502792107136</v>
       </c>
     </row>
     <row r="23">
@@ -871,10 +871,10 @@
         <v>26</v>
       </c>
       <c r="C23" t="n">
-        <v>0.4088185973569</v>
+        <v>0.408909389303892</v>
       </c>
       <c r="D23" t="n">
-        <v>0.288546878914999</v>
+        <v>0.288611410677035</v>
       </c>
     </row>
     <row r="24">
@@ -885,10 +885,10 @@
         <v>27</v>
       </c>
       <c r="C24" t="n">
-        <v>0.408679452039316</v>
+        <v>0.408669529054326</v>
       </c>
       <c r="D24" t="n">
-        <v>0.0216180208798748</v>
+        <v>0.0216113595371055</v>
       </c>
     </row>
     <row r="25">
@@ -899,10 +899,10 @@
         <v>28</v>
       </c>
       <c r="C25" t="n">
-        <v>0.271640061510356</v>
+        <v>0.271861567131855</v>
       </c>
       <c r="D25" t="n">
-        <v>0.0725397552414903</v>
+        <v>0.0725781789921531</v>
       </c>
     </row>
     <row r="26">
@@ -913,10 +913,10 @@
         <v>29</v>
       </c>
       <c r="C26" t="n">
-        <v>0.24651846614152</v>
+        <v>0.246721509220616</v>
       </c>
       <c r="D26" t="n">
-        <v>0.016108691495076</v>
+        <v>0.0161258643029431</v>
       </c>
     </row>
     <row r="27">
@@ -927,10 +927,10 @@
         <v>30</v>
       </c>
       <c r="C27" t="n">
-        <v>0.243813579955803</v>
+        <v>0.243879591581764</v>
       </c>
       <c r="D27" t="n">
-        <v>0.0101626459904186</v>
+        <v>0.0101684375210739</v>
       </c>
     </row>
     <row r="28">
@@ -941,10 +941,10 @@
         <v>31</v>
       </c>
       <c r="C28" t="n">
-        <v>0.224707900679495</v>
+        <v>0.224925583357573</v>
       </c>
       <c r="D28" t="n">
-        <v>0.0481322120250368</v>
+        <v>0.048230329885155</v>
       </c>
     </row>
     <row r="29">
@@ -955,10 +955,10 @@
         <v>32</v>
       </c>
       <c r="C29" t="n">
-        <v>0.201662483669726</v>
+        <v>0.201956720680122</v>
       </c>
       <c r="D29" t="n">
-        <v>0.113021158477521</v>
+        <v>0.113189572684481</v>
       </c>
     </row>
     <row r="30">
@@ -969,10 +969,10 @@
         <v>33</v>
       </c>
       <c r="C30" t="n">
-        <v>0.181341093044664</v>
+        <v>0.181297270181016</v>
       </c>
       <c r="D30" t="n">
-        <v>0.0366730244195918</v>
+        <v>0.0366559937521825</v>
       </c>
     </row>
     <row r="31">
@@ -983,7 +983,7 @@
         <v>34</v>
       </c>
       <c r="C31" t="n">
-        <v>0.155636591615676</v>
+        <v>0.155646191017779</v>
       </c>
       <c r="D31"/>
     </row>
@@ -995,10 +995,10 @@
         <v>35</v>
       </c>
       <c r="C32" t="n">
-        <v>0.136854555704109</v>
+        <v>0.136954032102515</v>
       </c>
       <c r="D32" t="n">
-        <v>0.0099182769151916</v>
+        <v>0.00992803048451358</v>
       </c>
     </row>
     <row r="33">
@@ -1009,10 +1009,10 @@
         <v>36</v>
       </c>
       <c r="C33" t="n">
-        <v>0.105939654299032</v>
+        <v>0.106073371239914</v>
       </c>
       <c r="D33" t="n">
-        <v>0.0346530973988826</v>
+        <v>0.0347010905517151</v>
       </c>
     </row>
     <row r="34">
@@ -1023,10 +1023,10 @@
         <v>37</v>
       </c>
       <c r="C34" t="n">
-        <v>0.105448800808803</v>
+        <v>0.105455041134451</v>
       </c>
       <c r="D34" t="n">
-        <v>0.0413991437900736</v>
+        <v>0.0414242815338174</v>
       </c>
     </row>
     <row r="35">
@@ -1037,10 +1037,10 @@
         <v>38</v>
       </c>
       <c r="C35" t="n">
-        <v>0.0779468045632271</v>
+        <v>0.0779402209067128</v>
       </c>
       <c r="D35" t="n">
-        <v>0.0104797531351658</v>
+        <v>0.0104788399728233</v>
       </c>
     </row>
     <row r="36">
@@ -1051,10 +1051,10 @@
         <v>39</v>
       </c>
       <c r="C36" t="n">
-        <v>0.074382854607591</v>
+        <v>0.0744314513860011</v>
       </c>
       <c r="D36" t="n">
-        <v>0.00497512625900137</v>
+        <v>0.00497928913366611</v>
       </c>
     </row>
     <row r="37">
@@ -1065,10 +1065,10 @@
         <v>40</v>
       </c>
       <c r="C37" t="n">
-        <v>0.0695745671991399</v>
+        <v>0.0696031139254447</v>
       </c>
       <c r="D37" t="n">
-        <v>0.0095372186779335</v>
+        <v>0.0095375980362307</v>
       </c>
     </row>
     <row r="38">
@@ -1079,10 +1079,10 @@
         <v>41</v>
       </c>
       <c r="C38" t="n">
-        <v>0.0682203840881914</v>
+        <v>0.0681926728321165</v>
       </c>
       <c r="D38" t="n">
-        <v>0.0142143920882456</v>
+        <v>0.0142057188553385</v>
       </c>
     </row>
     <row r="39">
@@ -1093,10 +1093,10 @@
         <v>42</v>
       </c>
       <c r="C39" t="n">
-        <v>0.0507339880982861</v>
+        <v>0.0507395300984238</v>
       </c>
       <c r="D39" t="n">
-        <v>0.0176436675496659</v>
+        <v>0.0176397754207485</v>
       </c>
     </row>
     <row r="40">
@@ -1107,10 +1107,10 @@
         <v>43</v>
       </c>
       <c r="C40" t="n">
-        <v>0.0475084997259635</v>
+        <v>0.0475787150042916</v>
       </c>
       <c r="D40" t="n">
-        <v>0.00765797872765387</v>
+        <v>0.00767280656412586</v>
       </c>
     </row>
     <row r="41">
@@ -1121,10 +1121,10 @@
         <v>44</v>
       </c>
       <c r="C41" t="n">
-        <v>0.0429041873413532</v>
+        <v>0.0429446890274804</v>
       </c>
       <c r="D41" t="n">
-        <v>0.00545126739233153</v>
+        <v>0.00545621228072605</v>
       </c>
     </row>
     <row r="42">
@@ -1135,10 +1135,10 @@
         <v>45</v>
       </c>
       <c r="C42" t="n">
-        <v>0.0401596736468768</v>
+        <v>0.040181023270795</v>
       </c>
       <c r="D42" t="n">
-        <v>0.000909775279952365</v>
+        <v>0.000910029833040341</v>
       </c>
     </row>
     <row r="43">
@@ -1149,10 +1149,10 @@
         <v>46</v>
       </c>
       <c r="C43" t="n">
-        <v>0.0333910032767665</v>
+        <v>0.0334073832857585</v>
       </c>
       <c r="D43" t="n">
-        <v>0.0159828163430173</v>
+        <v>0.0159679892239189</v>
       </c>
     </row>
     <row r="44">
@@ -1163,10 +1163,10 @@
         <v>47</v>
       </c>
       <c r="C44" t="n">
-        <v>0.0321269081991875</v>
+        <v>0.0321347664752137</v>
       </c>
       <c r="D44" t="n">
-        <v>0.00507130742080848</v>
+        <v>0.00507233486298088</v>
       </c>
     </row>
     <row r="45">
@@ -1177,10 +1177,10 @@
         <v>48</v>
       </c>
       <c r="C45" t="n">
-        <v>0.0259404142042226</v>
+        <v>0.0259715472656145</v>
       </c>
       <c r="D45" t="n">
-        <v>0.000584390141011398</v>
+        <v>0.000559194759903937</v>
       </c>
     </row>
     <row r="46">
@@ -1191,10 +1191,10 @@
         <v>49</v>
       </c>
       <c r="C46" t="n">
-        <v>0.0243285961567221</v>
+        <v>0.0243343159503515</v>
       </c>
       <c r="D46" t="n">
-        <v>0.00553670954351923</v>
+        <v>0.00553543484028905</v>
       </c>
     </row>
     <row r="47">
@@ -1205,10 +1205,10 @@
         <v>50</v>
       </c>
       <c r="C47" t="n">
-        <v>0.0234303539149701</v>
+        <v>0.0234492002165133</v>
       </c>
       <c r="D47" t="n">
-        <v>0.00430143010827285</v>
+        <v>0.00430577401358512</v>
       </c>
     </row>
     <row r="48">
@@ -1219,7 +1219,7 @@
         <v>51</v>
       </c>
       <c r="C48" t="n">
-        <v>0.0207110985476066</v>
+        <v>0.0207233421792403</v>
       </c>
       <c r="D48"/>
     </row>
@@ -1231,10 +1231,10 @@
         <v>52</v>
       </c>
       <c r="C49" t="n">
-        <v>0.0157348713286623</v>
+        <v>0.0157339012021377</v>
       </c>
       <c r="D49" t="n">
-        <v>0.00281262510809732</v>
+        <v>0.00281091466530258</v>
       </c>
     </row>
     <row r="50">
@@ -1245,7 +1245,7 @@
         <v>53</v>
       </c>
       <c r="C50" t="n">
-        <v>0.0134256428047656</v>
+        <v>0.0134533216169343</v>
       </c>
       <c r="D50"/>
     </row>
@@ -1257,10 +1257,10 @@
         <v>54</v>
       </c>
       <c r="C51" t="n">
-        <v>0.0128806242352841</v>
+        <v>0.0128961906537249</v>
       </c>
       <c r="D51" t="n">
-        <v>0.000372288747805415</v>
+        <v>0.00037590358487797</v>
       </c>
     </row>
     <row r="52">
@@ -1271,10 +1271,10 @@
         <v>55</v>
       </c>
       <c r="C52" t="n">
-        <v>0.00602035033217753</v>
+        <v>0.00601922452750512</v>
       </c>
       <c r="D52" t="n">
-        <v>0.00110838153685583</v>
+        <v>0.0011078502016437</v>
       </c>
     </row>
     <row r="53">
@@ -1285,10 +1285,10 @@
         <v>56</v>
       </c>
       <c r="C53" t="n">
-        <v>0.00500530235993212</v>
+        <v>0.0050069424733291</v>
       </c>
       <c r="D53" t="n">
-        <v>0.00300775968935928</v>
+        <v>0.00300925158530516</v>
       </c>
     </row>
     <row r="54">
@@ -1299,7 +1299,7 @@
         <v>57</v>
       </c>
       <c r="C54" t="n">
-        <v>0.00472970594632202</v>
+        <v>0.00473258408216348</v>
       </c>
       <c r="D54"/>
     </row>
@@ -1311,10 +1311,10 @@
         <v>58</v>
       </c>
       <c r="C55" t="n">
-        <v>0.00400002094083704</v>
+        <v>0.00399881141505295</v>
       </c>
       <c r="D55" t="n">
-        <v>0.00110559438793898</v>
+        <v>0.00110581576899999</v>
       </c>
     </row>
     <row r="56">
@@ -1325,10 +1325,10 @@
         <v>59</v>
       </c>
       <c r="C56" t="n">
-        <v>0.00326994302804142</v>
+        <v>0.00327564061584886</v>
       </c>
       <c r="D56" t="n">
-        <v>0.000561630333743158</v>
+        <v>0.000562086716672459</v>
       </c>
     </row>
     <row r="57">
@@ -1339,10 +1339,10 @@
         <v>60</v>
       </c>
       <c r="C57" t="n">
-        <v>0.00308701661012792</v>
+        <v>0.00308508746622922</v>
       </c>
       <c r="D57" t="n">
-        <v>0.00111988265544537</v>
+        <v>0.00111918281638882</v>
       </c>
     </row>
     <row r="58">
@@ -1353,10 +1353,10 @@
         <v>61</v>
       </c>
       <c r="C58" t="n">
-        <v>0.00174619234774136</v>
+        <v>0.00174779365200135</v>
       </c>
       <c r="D58" t="n">
-        <v>0.000437459123487345</v>
+        <v>0.000439089657549766</v>
       </c>
     </row>
     <row r="59">
@@ -1367,10 +1367,10 @@
         <v>62</v>
       </c>
       <c r="C59" t="n">
-        <v>0.00158700875731402</v>
+        <v>0.00159011190234553</v>
       </c>
       <c r="D59" t="n">
-        <v>0.0000335774286400194</v>
+        <v>0.0000354206923389287</v>
       </c>
     </row>
     <row r="60">
@@ -1381,7 +1381,7 @@
         <v>63</v>
       </c>
       <c r="C60" t="n">
-        <v>0.00123771415814994</v>
+        <v>0.00123828695256209</v>
       </c>
       <c r="D60"/>
     </row>
@@ -1393,7 +1393,7 @@
         <v>64</v>
       </c>
       <c r="C61" t="n">
-        <v>0.0011462790140011</v>
+        <v>0.00114589924652043</v>
       </c>
       <c r="D61"/>
     </row>
@@ -1405,7 +1405,7 @@
         <v>65</v>
       </c>
       <c r="C62" t="n">
-        <v>0.000865125768426153</v>
+        <v>0.000865370456044187</v>
       </c>
       <c r="D62"/>
     </row>
@@ -1417,7 +1417,7 @@
         <v>66</v>
       </c>
       <c r="C63" t="n">
-        <v>0.000326898882457271</v>
+        <v>0.000328040865167978</v>
       </c>
       <c r="D63"/>
     </row>
@@ -1454,10 +1454,10 @@
         <v>15</v>
       </c>
       <c r="C2" t="n">
-        <v>22.7061117486256</v>
+        <v>23.4705454933668</v>
       </c>
       <c r="D2" t="n">
-        <v>5.79726987987374</v>
+        <v>5.99250419784372</v>
       </c>
     </row>
     <row r="3">
@@ -1468,10 +1468,10 @@
         <v>5</v>
       </c>
       <c r="C3" t="n">
-        <v>20.0031549773461</v>
+        <v>20.4859212834771</v>
       </c>
       <c r="D3" t="n">
-        <v>0.425374345745762</v>
+        <v>0.437114722338211</v>
       </c>
     </row>
     <row r="4">
@@ -1482,10 +1482,10 @@
         <v>14</v>
       </c>
       <c r="C4" t="n">
-        <v>17.2289684631037</v>
+        <v>16.7914816095962</v>
       </c>
       <c r="D4" t="n">
-        <v>1.35640166310062</v>
+        <v>1.31249597273238</v>
       </c>
     </row>
     <row r="5">
@@ -1496,10 +1496,10 @@
         <v>18</v>
       </c>
       <c r="C5" t="n">
-        <v>15.3572206618281</v>
+        <v>15.7930064167728</v>
       </c>
       <c r="D5" t="n">
-        <v>1.44600602724275</v>
+        <v>1.48639201031792</v>
       </c>
     </row>
     <row r="6">
@@ -1510,10 +1510,10 @@
         <v>22</v>
       </c>
       <c r="C6" t="n">
-        <v>3.75476841889558</v>
+        <v>3.81496895064517</v>
       </c>
       <c r="D6" t="n">
-        <v>0.359997513227149</v>
+        <v>0.367651838161368</v>
       </c>
     </row>
     <row r="7">
@@ -1521,13 +1521,13 @@
         <v>67</v>
       </c>
       <c r="B7" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C7" t="n">
-        <v>3.75065572403296</v>
+        <v>2.96867506373935</v>
       </c>
       <c r="D7" t="n">
-        <v>0.374081912335686</v>
+        <v>0.123661905458887</v>
       </c>
     </row>
     <row r="8">
@@ -1535,13 +1535,13 @@
         <v>67</v>
       </c>
       <c r="B8" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="C8" t="n">
-        <v>2.91971870255401</v>
+        <v>2.73867676773483</v>
       </c>
       <c r="D8" t="n">
-        <v>0.120664663137462</v>
+        <v>0.0757142681873042</v>
       </c>
     </row>
     <row r="9">
@@ -1549,13 +1549,13 @@
         <v>67</v>
       </c>
       <c r="B9" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="C9" t="n">
-        <v>2.66473431247248</v>
+        <v>2.52866516711127</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0735885333183153</v>
+        <v>0.140185896636978</v>
       </c>
     </row>
     <row r="10">
@@ -1563,13 +1563,13 @@
         <v>67</v>
       </c>
       <c r="B10" t="s">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="C10" t="n">
-        <v>2.45993150481413</v>
+        <v>2.35101799115643</v>
       </c>
       <c r="D10" t="n">
-        <v>0.136362620703838</v>
+        <v>0.0396077727816633</v>
       </c>
     </row>
     <row r="11">
@@ -1577,13 +1577,13 @@
         <v>67</v>
       </c>
       <c r="B11" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="C11" t="n">
-        <v>2.34900722367891</v>
+        <v>2.15291359848522</v>
       </c>
       <c r="D11" t="n">
-        <v>0.040785838738848</v>
+        <v>0.227681151887976</v>
       </c>
     </row>
     <row r="12">
@@ -1594,10 +1594,10 @@
         <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>1.29153462348307</v>
+        <v>1.32739437688393</v>
       </c>
       <c r="D12" t="n">
-        <v>0.0501093806185089</v>
+        <v>0.0515430421464025</v>
       </c>
     </row>
     <row r="13">
@@ -1608,10 +1608,10 @@
         <v>17</v>
       </c>
       <c r="C13" t="n">
-        <v>1.03920553458732</v>
+        <v>1.0647315831229</v>
       </c>
       <c r="D13" t="n">
-        <v>0.172097503308188</v>
+        <v>0.177254928227554</v>
       </c>
     </row>
     <row r="14">
@@ -1622,10 +1622,10 @@
         <v>8</v>
       </c>
       <c r="C14" t="n">
-        <v>1.01589747478353</v>
+        <v>1.0419230223091</v>
       </c>
       <c r="D14" t="n">
-        <v>0.0317534985613793</v>
+        <v>0.0325945325146695</v>
       </c>
     </row>
     <row r="15">
@@ -1636,10 +1636,10 @@
         <v>13</v>
       </c>
       <c r="C15" t="n">
-        <v>0.830670338738606</v>
+        <v>0.823828086395262</v>
       </c>
       <c r="D15" t="n">
-        <v>0.0391804644561111</v>
+        <v>0.0379236148869747</v>
       </c>
     </row>
     <row r="16">
@@ -1650,10 +1650,10 @@
         <v>27</v>
       </c>
       <c r="C16" t="n">
-        <v>0.694618376644597</v>
+        <v>0.689706418633628</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0766116524973975</v>
+        <v>0.0750216326489843</v>
       </c>
     </row>
     <row r="17">
@@ -1664,10 +1664,10 @@
         <v>24</v>
       </c>
       <c r="C17" t="n">
-        <v>0.320125364712708</v>
+        <v>0.318880834425252</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0190318572558435</v>
+        <v>0.0185172484108917</v>
       </c>
     </row>
     <row r="18">
@@ -1675,13 +1675,13 @@
         <v>67</v>
       </c>
       <c r="B18" t="s">
-        <v>35</v>
+        <v>16</v>
       </c>
       <c r="C18" t="n">
-        <v>0.269376189208359</v>
+        <v>0.268895247462936</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0361749133342765</v>
+        <v>0.0266037353472046</v>
       </c>
     </row>
     <row r="19">
@@ -1689,13 +1689,13 @@
         <v>67</v>
       </c>
       <c r="B19" t="s">
-        <v>16</v>
+        <v>35</v>
       </c>
       <c r="C19" t="n">
-        <v>0.261155187637025</v>
+        <v>0.268566736272459</v>
       </c>
       <c r="D19" t="n">
-        <v>0.0258603339415769</v>
+        <v>0.0351811649083005</v>
       </c>
     </row>
     <row r="20">
@@ -1706,10 +1706,10 @@
         <v>30</v>
       </c>
       <c r="C20" t="n">
-        <v>0.162051188928205</v>
+        <v>0.167176062126895</v>
       </c>
       <c r="D20" t="n">
-        <v>0.019694383033903</v>
+        <v>0.0203470654640061</v>
       </c>
     </row>
     <row r="21">
@@ -1720,10 +1720,10 @@
         <v>45</v>
       </c>
       <c r="C21" t="n">
-        <v>0.157610669714087</v>
+        <v>0.161233460630196</v>
       </c>
       <c r="D21" t="n">
-        <v>0.00539666022118281</v>
+        <v>0.00548458040232496</v>
       </c>
     </row>
     <row r="22">
@@ -1731,13 +1731,13 @@
         <v>67</v>
       </c>
       <c r="B22" t="s">
-        <v>39</v>
+        <v>20</v>
       </c>
       <c r="C22" t="n">
-        <v>0.109550262382671</v>
+        <v>0.107991139742958</v>
       </c>
       <c r="D22" t="n">
-        <v>0.025280811939818</v>
+        <v>0.0410110682613569</v>
       </c>
     </row>
     <row r="23">
@@ -1745,13 +1745,13 @@
         <v>67</v>
       </c>
       <c r="B23" t="s">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="C23" t="n">
-        <v>0.10491414852157</v>
+        <v>0.106884759265806</v>
       </c>
       <c r="D23" t="n">
-        <v>0.0398425121150081</v>
+        <v>0.0241702592492542</v>
       </c>
     </row>
     <row r="24">
@@ -1759,13 +1759,13 @@
         <v>67</v>
       </c>
       <c r="B24" t="s">
-        <v>49</v>
+        <v>26</v>
       </c>
       <c r="C24" t="n">
-        <v>0.0855498104004779</v>
+        <v>0.086594263181063</v>
       </c>
       <c r="D24" t="n">
-        <v>0.018952200334533</v>
+        <v>0.0371737281396527</v>
       </c>
     </row>
     <row r="25">
@@ -1773,13 +1773,13 @@
         <v>67</v>
       </c>
       <c r="B25" t="s">
-        <v>26</v>
+        <v>49</v>
       </c>
       <c r="C25" t="n">
-        <v>0.0840533914081825</v>
+        <v>0.0844880398968756</v>
       </c>
       <c r="D25" t="n">
-        <v>0.0362293004451723</v>
+        <v>0.0182260456200026</v>
       </c>
     </row>
     <row r="26">
@@ -1790,10 +1790,10 @@
         <v>33</v>
       </c>
       <c r="C26" t="n">
-        <v>0.076994197466267</v>
+        <v>0.0791553244756159</v>
       </c>
       <c r="D26" t="n">
-        <v>0.0310143979014056</v>
+        <v>0.0318742477443166</v>
       </c>
     </row>
     <row r="27">
@@ -1804,10 +1804,10 @@
         <v>25</v>
       </c>
       <c r="C27" t="n">
-        <v>0.073951978123</v>
+        <v>0.0764200359304541</v>
       </c>
       <c r="D27" t="n">
-        <v>0.00793441779774488</v>
+        <v>0.00821806387958583</v>
       </c>
     </row>
     <row r="28">
@@ -1818,10 +1818,10 @@
         <v>44</v>
       </c>
       <c r="C28" t="n">
-        <v>0.0704477154272872</v>
+        <v>0.0674992496203779</v>
       </c>
       <c r="D28" t="n">
-        <v>0.0480220743087568</v>
+        <v>0.0458877574879519</v>
       </c>
     </row>
     <row r="29">
@@ -1832,10 +1832,10 @@
         <v>9</v>
       </c>
       <c r="C29" t="n">
-        <v>0.0458593093297682</v>
+        <v>0.0472195155237567</v>
       </c>
       <c r="D29" t="n">
-        <v>0.00468007494878991</v>
+        <v>0.00481573325923385</v>
       </c>
     </row>
     <row r="30">
@@ -1846,10 +1846,10 @@
         <v>23</v>
       </c>
       <c r="C30" t="n">
-        <v>0.0383163653007281</v>
+        <v>0.0394404619199695</v>
       </c>
       <c r="D30" t="n">
-        <v>0.0116189930360815</v>
+        <v>0.0119605398360741</v>
       </c>
     </row>
     <row r="31">
@@ -1860,7 +1860,7 @@
         <v>19</v>
       </c>
       <c r="C31" t="n">
-        <v>0.015617732312067</v>
+        <v>0.0161375110038096</v>
       </c>
       <c r="D31"/>
     </row>
@@ -1872,10 +1872,10 @@
         <v>37</v>
       </c>
       <c r="C32" t="n">
-        <v>0.0134894776653377</v>
+        <v>0.0138718419514769</v>
       </c>
       <c r="D32" t="n">
-        <v>0.0015631549446498</v>
+        <v>0.00160899961333783</v>
       </c>
     </row>
     <row r="33">
@@ -1886,10 +1886,10 @@
         <v>52</v>
       </c>
       <c r="C33" t="n">
-        <v>0.00881667883754306</v>
+        <v>0.00907013144132543</v>
       </c>
       <c r="D33" t="n">
-        <v>0.00332298168777018</v>
+        <v>0.00341833606605476</v>
       </c>
     </row>
     <row r="34">
@@ -1900,10 +1900,10 @@
         <v>47</v>
       </c>
       <c r="C34" t="n">
-        <v>0.00869187974032043</v>
+        <v>0.00898493737893408</v>
       </c>
       <c r="D34" t="n">
-        <v>0.00194692079877922</v>
+        <v>0.00203098630084255</v>
       </c>
     </row>
     <row r="35">
@@ -1914,7 +1914,7 @@
         <v>51</v>
       </c>
       <c r="C35" t="n">
-        <v>0.00732417992940791</v>
+        <v>0.0075438530589213</v>
       </c>
       <c r="D35"/>
     </row>
@@ -1926,7 +1926,7 @@
         <v>50</v>
       </c>
       <c r="C36" t="n">
-        <v>0.00428681680980228</v>
+        <v>0.00441079181313773</v>
       </c>
       <c r="D36"/>
     </row>
@@ -1938,10 +1938,10 @@
         <v>43</v>
       </c>
       <c r="C37" t="n">
-        <v>0.00398268848942568</v>
+        <v>0.00409785243787524</v>
       </c>
       <c r="D37" t="n">
-        <v>0.000436981159106562</v>
+        <v>0.000449912059585068</v>
       </c>
     </row>
     <row r="38">
@@ -1952,7 +1952,7 @@
         <v>40</v>
       </c>
       <c r="C38" t="n">
-        <v>0.00353486275565068</v>
+        <v>0.00363851395045826</v>
       </c>
       <c r="D38"/>
     </row>
@@ -1964,10 +1964,10 @@
         <v>29</v>
       </c>
       <c r="C39" t="n">
-        <v>0.00270579421010695</v>
+        <v>0.00278434878151413</v>
       </c>
       <c r="D39" t="n">
-        <v>0.000487424423054235</v>
+        <v>0.000502086754441095</v>
       </c>
     </row>
     <row r="40">
@@ -1978,10 +1978,10 @@
         <v>36</v>
       </c>
       <c r="C40" t="n">
-        <v>0.00216973732836583</v>
+        <v>0.00223338308796842</v>
       </c>
       <c r="D40" t="n">
-        <v>0.0000654503645140934</v>
+        <v>0.0000673835280772706</v>
       </c>
     </row>
     <row r="41">
@@ -1992,7 +1992,7 @@
         <v>68</v>
       </c>
       <c r="C41" t="n">
-        <v>0.00149103619016489</v>
+        <v>0.00153806245878289</v>
       </c>
       <c r="D41"/>
     </row>
@@ -2004,7 +2004,7 @@
         <v>57</v>
       </c>
       <c r="C42" t="n">
-        <v>0.000989733487397163</v>
+        <v>0.00101878150121476</v>
       </c>
       <c r="D42"/>
     </row>
@@ -2016,7 +2016,7 @@
         <v>64</v>
       </c>
       <c r="C43" t="n">
-        <v>0.000745518095082446</v>
+        <v>0.000769031229391446</v>
       </c>
       <c r="D43"/>
     </row>
@@ -2053,10 +2053,10 @@
         <v>6</v>
       </c>
       <c r="C2" t="n">
-        <v>29.2696693710857</v>
+        <v>29.2708263490043</v>
       </c>
       <c r="D2" t="n">
-        <v>0.323657020352679</v>
+        <v>0.323690875706401</v>
       </c>
     </row>
     <row r="3">
@@ -2067,10 +2067,10 @@
         <v>5</v>
       </c>
       <c r="C3" t="n">
-        <v>13.5624767849073</v>
+        <v>13.5626620658277</v>
       </c>
       <c r="D3" t="n">
-        <v>0.164418843472401</v>
+        <v>0.164951302180931</v>
       </c>
     </row>
     <row r="4">
@@ -2081,10 +2081,10 @@
         <v>7</v>
       </c>
       <c r="C4" t="n">
-        <v>10.3175885257203</v>
+        <v>10.3168263706702</v>
       </c>
       <c r="D4" t="n">
-        <v>0.122586489858399</v>
+        <v>0.122574627361324</v>
       </c>
     </row>
     <row r="5">
@@ -2095,10 +2095,10 @@
         <v>12</v>
       </c>
       <c r="C5" t="n">
-        <v>9.30586667012119</v>
+        <v>9.30577787924505</v>
       </c>
       <c r="D5" t="n">
-        <v>0.167019150095391</v>
+        <v>0.16701269751572</v>
       </c>
     </row>
     <row r="6">
@@ -2109,10 +2109,10 @@
         <v>9</v>
       </c>
       <c r="C6" t="n">
-        <v>4.06888660098701</v>
+        <v>4.0689240038311</v>
       </c>
       <c r="D6" t="n">
-        <v>0.313814867117275</v>
+        <v>0.313821955887357</v>
       </c>
     </row>
     <row r="7">
@@ -2123,10 +2123,10 @@
         <v>10</v>
       </c>
       <c r="C7" t="n">
-        <v>3.99447670452437</v>
+        <v>3.99479813533576</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0922713128025324</v>
+        <v>0.0922830964972073</v>
       </c>
     </row>
     <row r="8">
@@ -2137,10 +2137,10 @@
         <v>13</v>
       </c>
       <c r="C8" t="n">
-        <v>3.7243080649101</v>
+        <v>3.72399152550915</v>
       </c>
       <c r="D8" t="n">
-        <v>0.053899320325139</v>
+        <v>0.0538939796108262</v>
       </c>
     </row>
     <row r="9">
@@ -2151,10 +2151,10 @@
         <v>14</v>
       </c>
       <c r="C9" t="n">
-        <v>3.18513984798712</v>
+        <v>3.18497137478922</v>
       </c>
       <c r="D9" t="n">
-        <v>0.114016331705178</v>
+        <v>0.114008461300709</v>
       </c>
     </row>
     <row r="10">
@@ -2165,10 +2165,10 @@
         <v>8</v>
       </c>
       <c r="C10" t="n">
-        <v>3.04891292336428</v>
+        <v>3.04910811408604</v>
       </c>
       <c r="D10" t="n">
-        <v>0.0562950685147359</v>
+        <v>0.0562993834594735</v>
       </c>
     </row>
     <row r="11">
@@ -2179,10 +2179,10 @@
         <v>33</v>
       </c>
       <c r="C11" t="n">
-        <v>2.90693837065784</v>
+        <v>2.9078237697701</v>
       </c>
       <c r="D11" t="n">
-        <v>0.848514761712234</v>
+        <v>0.848774383302174</v>
       </c>
     </row>
     <row r="12">
@@ -2193,10 +2193,10 @@
         <v>15</v>
       </c>
       <c r="C12" t="n">
-        <v>1.92601490170582</v>
+        <v>1.92605377647559</v>
       </c>
       <c r="D12" t="n">
-        <v>0.117513743520371</v>
+        <v>0.117520824848877</v>
       </c>
     </row>
     <row r="13">
@@ -2207,10 +2207,10 @@
         <v>18</v>
       </c>
       <c r="C13" t="n">
-        <v>1.75106759017128</v>
+        <v>1.75138898300309</v>
       </c>
       <c r="D13" t="n">
-        <v>0.1667718000852</v>
+        <v>0.166801682503198</v>
       </c>
     </row>
     <row r="14">
@@ -2221,10 +2221,10 @@
         <v>24</v>
       </c>
       <c r="C14" t="n">
-        <v>1.66227348891857</v>
+        <v>1.66241700859943</v>
       </c>
       <c r="D14" t="n">
-        <v>0.0179556438162667</v>
+        <v>0.017957952356141</v>
       </c>
     </row>
     <row r="15">
@@ -2235,10 +2235,10 @@
         <v>31</v>
       </c>
       <c r="C15" t="n">
-        <v>1.55734061781472</v>
+        <v>1.55728726615353</v>
       </c>
       <c r="D15" t="n">
-        <v>0.522080141675004</v>
+        <v>0.522067960073351</v>
       </c>
     </row>
     <row r="16">
@@ -2249,10 +2249,10 @@
         <v>20</v>
       </c>
       <c r="C16" t="n">
-        <v>1.23047170899452</v>
+        <v>1.230360372418</v>
       </c>
       <c r="D16" t="n">
-        <v>0.151613823845976</v>
+        <v>0.151602610044505</v>
       </c>
     </row>
     <row r="17">
@@ -2263,10 +2263,10 @@
         <v>11</v>
       </c>
       <c r="C17" t="n">
-        <v>1.10164084860228</v>
+        <v>1.0999985026971</v>
       </c>
       <c r="D17" t="n">
-        <v>0.116595329532773</v>
+        <v>0.122485387874707</v>
       </c>
     </row>
     <row r="18">
@@ -2277,10 +2277,10 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>0.953034434585218</v>
+        <v>0.953081885062691</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0973706636466204</v>
+        <v>0.0973790540227632</v>
       </c>
     </row>
     <row r="19">
@@ -2291,10 +2291,10 @@
         <v>37</v>
       </c>
       <c r="C19" t="n">
-        <v>0.848467110325538</v>
+        <v>0.84830527092907</v>
       </c>
       <c r="D19" t="n">
-        <v>0.289379225813157</v>
+        <v>0.289314746281158</v>
       </c>
     </row>
     <row r="20">
@@ -2305,10 +2305,10 @@
         <v>42</v>
       </c>
       <c r="C20" t="n">
-        <v>0.546939917718448</v>
+        <v>0.5469106672692</v>
       </c>
       <c r="D20" t="n">
-        <v>0.236708808884444</v>
+        <v>0.23669411707758</v>
       </c>
     </row>
     <row r="21">
@@ -2319,10 +2319,10 @@
         <v>19</v>
       </c>
       <c r="C21" t="n">
-        <v>0.430293030354796</v>
+        <v>0.430362935082194</v>
       </c>
       <c r="D21" t="n">
-        <v>0.106578730709796</v>
+        <v>0.106595560404305</v>
       </c>
     </row>
     <row r="22">
@@ -2333,10 +2333,10 @@
         <v>35</v>
       </c>
       <c r="C22" t="n">
-        <v>0.419048522431741</v>
+        <v>0.419020322211645</v>
       </c>
       <c r="D22" t="n">
-        <v>0.0232657073408555</v>
+        <v>0.0232625777419894</v>
       </c>
     </row>
     <row r="23">
@@ -2347,10 +2347,10 @@
         <v>16</v>
       </c>
       <c r="C23" t="n">
-        <v>0.408266721626298</v>
+        <v>0.408321587683296</v>
       </c>
       <c r="D23" t="n">
-        <v>0.0234940178096526</v>
+        <v>0.0234985282277792</v>
       </c>
     </row>
     <row r="24">
@@ -2361,10 +2361,10 @@
         <v>21</v>
       </c>
       <c r="C24" t="n">
-        <v>0.372071007050711</v>
+        <v>0.372087649602625</v>
       </c>
       <c r="D24" t="n">
-        <v>0.0183126347282866</v>
+        <v>0.018315556326914</v>
       </c>
     </row>
     <row r="25">
@@ -2375,10 +2375,10 @@
         <v>45</v>
       </c>
       <c r="C25" t="n">
-        <v>0.346401561761411</v>
+        <v>0.346406996330817</v>
       </c>
       <c r="D25" t="n">
-        <v>0.00848242083577107</v>
+        <v>0.00848308271124754</v>
       </c>
     </row>
     <row r="26">
@@ -2389,10 +2389,10 @@
         <v>36</v>
       </c>
       <c r="C26" t="n">
-        <v>0.310150166875274</v>
+        <v>0.310114714012385</v>
       </c>
       <c r="D26" t="n">
-        <v>0.0685769544517772</v>
+        <v>0.0685672363066828</v>
       </c>
     </row>
     <row r="27">
@@ -2403,10 +2403,10 @@
         <v>25</v>
       </c>
       <c r="C27" t="n">
-        <v>0.295566559308626</v>
+        <v>0.295571086745162</v>
       </c>
       <c r="D27" t="n">
-        <v>0.00808169739661992</v>
+        <v>0.00808183984791037</v>
       </c>
     </row>
     <row r="28">
@@ -2417,10 +2417,10 @@
         <v>27</v>
       </c>
       <c r="C28" t="n">
-        <v>0.268374612534452</v>
+        <v>0.268367880451845</v>
       </c>
       <c r="D28" t="n">
-        <v>0.00445395544917261</v>
+        <v>0.0044535770587391</v>
       </c>
     </row>
     <row r="29">
@@ -2431,10 +2431,10 @@
         <v>29</v>
       </c>
       <c r="C29" t="n">
-        <v>0.242674225434993</v>
+        <v>0.242650323142323</v>
       </c>
       <c r="D29" t="n">
-        <v>0.0224444037160852</v>
+        <v>0.0224418613647339</v>
       </c>
     </row>
     <row r="30">
@@ -2445,10 +2445,10 @@
         <v>28</v>
       </c>
       <c r="C30" t="n">
-        <v>0.235791615880213</v>
+        <v>0.235759726724195</v>
       </c>
       <c r="D30" t="n">
-        <v>0.0947939764946072</v>
+        <v>0.0947801490926459</v>
       </c>
     </row>
     <row r="31">
@@ -2459,10 +2459,10 @@
         <v>43</v>
       </c>
       <c r="C31" t="n">
-        <v>0.228626419407055</v>
+        <v>0.228594367045524</v>
       </c>
       <c r="D31" t="n">
-        <v>0.0299715373829527</v>
+        <v>0.0299670122309286</v>
       </c>
     </row>
     <row r="32">
@@ -2473,10 +2473,10 @@
         <v>41</v>
       </c>
       <c r="C32" t="n">
-        <v>0.213394528600517</v>
+        <v>0.213419785319753</v>
       </c>
       <c r="D32" t="n">
-        <v>0.0615196028841004</v>
+        <v>0.0615402836652481</v>
       </c>
     </row>
     <row r="33">
@@ -2487,10 +2487,10 @@
         <v>23</v>
       </c>
       <c r="C33" t="n">
-        <v>0.184825372319607</v>
+        <v>0.18480018114175</v>
       </c>
       <c r="D33" t="n">
-        <v>0.0604408082587919</v>
+        <v>0.0604306433345011</v>
       </c>
     </row>
     <row r="34">
@@ -2501,10 +2501,10 @@
         <v>30</v>
       </c>
       <c r="C34" t="n">
-        <v>0.18446535613716</v>
+        <v>0.18449359375152</v>
       </c>
       <c r="D34" t="n">
-        <v>0.00414895993143551</v>
+        <v>0.00414959037998375</v>
       </c>
     </row>
     <row r="35">
@@ -2515,10 +2515,10 @@
         <v>22</v>
       </c>
       <c r="C35" t="n">
-        <v>0.112034240751219</v>
+        <v>0.112029676930257</v>
       </c>
       <c r="D35" t="n">
-        <v>0.00554861862622549</v>
+        <v>0.00554800524943868</v>
       </c>
     </row>
     <row r="36">
@@ -2529,10 +2529,10 @@
         <v>50</v>
       </c>
       <c r="C36" t="n">
-        <v>0.0931332790647367</v>
+        <v>0.0931309996902721</v>
       </c>
       <c r="D36" t="n">
-        <v>0.0327415527241503</v>
+        <v>0.0327398335275147</v>
       </c>
     </row>
     <row r="37">
@@ -2543,10 +2543,10 @@
         <v>40</v>
       </c>
       <c r="C37" t="n">
-        <v>0.0904120440215771</v>
+        <v>0.0904003250131124</v>
       </c>
       <c r="D37" t="n">
-        <v>0.00899418206847615</v>
+        <v>0.00899305994560171</v>
       </c>
     </row>
     <row r="38">
@@ -2557,7 +2557,7 @@
         <v>26</v>
       </c>
       <c r="C38" t="n">
-        <v>0.0828081315444811</v>
+        <v>0.082792415700007</v>
       </c>
       <c r="D38"/>
     </row>
@@ -2569,10 +2569,10 @@
         <v>52</v>
       </c>
       <c r="C39" t="n">
-        <v>0.07513007830488</v>
+        <v>0.0751270586034985</v>
       </c>
       <c r="D39" t="n">
-        <v>0.00978986799512828</v>
+        <v>0.00978935660872495</v>
       </c>
     </row>
     <row r="40">
@@ -2583,10 +2583,10 @@
         <v>55</v>
       </c>
       <c r="C40" t="n">
-        <v>0.0555176044620979</v>
+        <v>0.0555219006253551</v>
       </c>
       <c r="D40" t="n">
-        <v>0.010882824261015</v>
+        <v>0.0108834020325943</v>
       </c>
     </row>
     <row r="41">
@@ -2597,10 +2597,10 @@
         <v>59</v>
       </c>
       <c r="C41" t="n">
-        <v>0.0443534406113147</v>
+        <v>0.044345580038103</v>
       </c>
       <c r="D41" t="n">
-        <v>0.00408391518117944</v>
+        <v>0.00408301381369857</v>
       </c>
     </row>
     <row r="42">
@@ -2611,10 +2611,10 @@
         <v>39</v>
       </c>
       <c r="C42" t="n">
-        <v>0.0439272059655816</v>
+        <v>0.0439311193068667</v>
       </c>
       <c r="D42" t="n">
-        <v>0.00281672021647584</v>
+        <v>0.00281725961473784</v>
       </c>
     </row>
     <row r="43">
@@ -2625,7 +2625,7 @@
         <v>51</v>
       </c>
       <c r="C43" t="n">
-        <v>0.0425454373998597</v>
+        <v>0.0425428850299084</v>
       </c>
       <c r="D43"/>
     </row>
@@ -2637,10 +2637,10 @@
         <v>62</v>
       </c>
       <c r="C44" t="n">
-        <v>0.0422022374185856</v>
+        <v>0.042212466894678</v>
       </c>
       <c r="D44" t="n">
-        <v>0.00704739422470973</v>
+        <v>0.00704998638812337</v>
       </c>
     </row>
     <row r="45">
@@ -2651,10 +2651,10 @@
         <v>46</v>
       </c>
       <c r="C45" t="n">
-        <v>0.0401099282992982</v>
+        <v>0.0401154360391381</v>
       </c>
       <c r="D45" t="n">
-        <v>0.00899770989979867</v>
+        <v>0.00899976873991183</v>
       </c>
     </row>
     <row r="46">
@@ -2665,10 +2665,10 @@
         <v>47</v>
       </c>
       <c r="C46" t="n">
-        <v>0.0397407192602098</v>
+        <v>0.0397402698905676</v>
       </c>
       <c r="D46" t="n">
-        <v>0.00804735726344126</v>
+        <v>0.00804510732230997</v>
       </c>
     </row>
     <row r="47">
@@ -2679,10 +2679,10 @@
         <v>49</v>
       </c>
       <c r="C47" t="n">
-        <v>0.0345161871410933</v>
+        <v>0.0345189461904412</v>
       </c>
       <c r="D47" t="n">
-        <v>0.00893760982438653</v>
+        <v>0.00893874389584192</v>
       </c>
     </row>
     <row r="48">
@@ -2693,10 +2693,10 @@
         <v>38</v>
       </c>
       <c r="C48" t="n">
-        <v>0.0240757178501265</v>
+        <v>0.0240772699490756</v>
       </c>
       <c r="D48" t="n">
-        <v>0.00316824594110922</v>
+        <v>0.00316770989894922</v>
       </c>
     </row>
     <row r="49">
@@ -2707,10 +2707,10 @@
         <v>44</v>
       </c>
       <c r="C49" t="n">
-        <v>0.0189050723134356</v>
+        <v>0.0189074176699697</v>
       </c>
       <c r="D49" t="n">
-        <v>0.00270797388873265</v>
+        <v>0.00270831467486109</v>
       </c>
     </row>
     <row r="50">
@@ -2721,10 +2721,10 @@
         <v>54</v>
       </c>
       <c r="C50" t="n">
-        <v>0.015449903512412</v>
+        <v>0.0154465809187106</v>
       </c>
       <c r="D50" t="n">
-        <v>0.00589527197923556</v>
+        <v>0.0058945862179202</v>
       </c>
     </row>
     <row r="51">
@@ -2735,10 +2735,10 @@
         <v>32</v>
       </c>
       <c r="C51" t="n">
-        <v>0.0102809022265025</v>
+        <v>0.0102788203664386</v>
       </c>
       <c r="D51" t="n">
-        <v>0.00662758978737952</v>
+        <v>0.00662641101662855</v>
       </c>
     </row>
     <row r="52">
@@ -2749,7 +2749,7 @@
         <v>70</v>
       </c>
       <c r="C52" t="n">
-        <v>0.00880533662757085</v>
+        <v>0.00880743994783173</v>
       </c>
       <c r="D52"/>
     </row>
@@ -2761,10 +2761,10 @@
         <v>57</v>
       </c>
       <c r="C53" t="n">
-        <v>0.00751019018255811</v>
+        <v>0.00751056931079806</v>
       </c>
       <c r="D53" t="n">
-        <v>0.00155233406502311</v>
+        <v>0.00155267126757225</v>
       </c>
     </row>
     <row r="54">
@@ -2775,7 +2775,7 @@
         <v>48</v>
       </c>
       <c r="C54" t="n">
-        <v>0.00730959158723154</v>
+        <v>0.00730789592149665</v>
       </c>
       <c r="D54"/>
     </row>
@@ -2787,7 +2787,7 @@
         <v>63</v>
       </c>
       <c r="C55" t="n">
-        <v>0.00305726011193323</v>
+        <v>0.00305638642701374</v>
       </c>
       <c r="D55"/>
     </row>
@@ -2799,7 +2799,7 @@
         <v>64</v>
       </c>
       <c r="C56" t="n">
-        <v>0.00177541715051518</v>
+        <v>0.00177542785482386</v>
       </c>
       <c r="D56"/>
     </row>
@@ -2811,10 +2811,10 @@
         <v>66</v>
       </c>
       <c r="C57" t="n">
-        <v>0.00172227795480832</v>
+        <v>0.00172358291115443</v>
       </c>
       <c r="D57" t="n">
-        <v>0.00017926116801792</v>
+        <v>0.00017928492614524</v>
       </c>
     </row>
     <row r="58">
@@ -2825,7 +2825,7 @@
         <v>68</v>
       </c>
       <c r="C58" t="n">
-        <v>0.00165785321964755</v>
+        <v>0.00165941172007079</v>
       </c>
       <c r="D58"/>
     </row>
@@ -2837,7 +2837,7 @@
         <v>58</v>
       </c>
       <c r="C59" t="n">
-        <v>0.00110359122898367</v>
+        <v>0.00110308708677645</v>
       </c>
       <c r="D59"/>
     </row>
@@ -2849,7 +2849,7 @@
         <v>60</v>
       </c>
       <c r="C60" t="n">
-        <v>0.000452168964875471</v>
+        <v>0.00045256004142569</v>
       </c>
       <c r="D60"/>
     </row>
